--- a/資料2/未入帳清單_11501.xlsx
+++ b/資料2/未入帳清單_11501.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1999"/>
+  <dimension ref="A1:K1999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="13.69921875" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -581,7 +581,6 @@
     <col width="14.3984375" bestFit="1" customWidth="1" style="6" min="9" max="9"/>
     <col width="10" bestFit="1" customWidth="1" style="6" min="10" max="10"/>
     <col width="10" customWidth="1" style="6" min="11" max="11"/>
-    <col width="12" customWidth="1" style="6" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="6">
@@ -694,11 +693,6 @@
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>待確認</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>經辦人</t>
         </is>
       </c>
     </row>
@@ -88236,7 +88230,6 @@
       <c r="J1972" s="15" t="n"/>
       <c r="K1972" s="15" t="n"/>
     </row>
-    <row r="1973"/>
     <row r="1974">
       <c r="A1974" s="16" t="inlineStr">
         <is>
